--- a/data/trans_dic/IP16A04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,78</t>
+          <t>0,0; 17,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,69</t>
+          <t>0,0; 15,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 7,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,72</t>
+          <t>0,0; 15,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,33</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,31</t>
+          <t>0,0; 42,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,0</t>
+          <t>0,0; 33,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,12</t>
+          <t>0,0; 22,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,4</t>
+          <t>0,0; 25,28</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,95</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,15</t>
+          <t>0,0; 29,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,16</t>
+          <t>0,0; 14,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,1</t>
+          <t>0,0; 36,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 23,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,23</t>
+          <t>0,0; 22,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,79</t>
+          <t>0,0; 22,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 15,21</t>
+          <t>1,94; 17,39</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>0,0; 9,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,28</t>
+          <t>0,0; 11,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1558,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1567,37 +1568,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,42</t>
+          <t>1,13; 5,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,59</t>
+          <t>0,47; 3,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,97</t>
+          <t>0,32; 2,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,69</t>
+          <t>0,51; 2,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,65</t>
+          <t>0,17; 1,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3428</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3910</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3173</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4196</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3276</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2756</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3586</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4302</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3623</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4982</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3485</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5062</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5059</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2594</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4852</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4781</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2995</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2885</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4041</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1542</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4436</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3079</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>654; 5857</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2689</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3069</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3043</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4994</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3177</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1836; 8510</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>673; 5186</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>605; 5577</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4940</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1371; 8042</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>628; 6243</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2576; 10070</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Provincia-trans_dic.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,53</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,91</t>
+          <t>0,0; 13,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,39</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,38</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,85</t>
+          <t>0,0; 37,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,87</t>
+          <t>0,0; 29,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,81</t>
+          <t>0,0; 22,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,28</t>
+          <t>0,0; 20,01</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,54</t>
+          <t>0,0; 28,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,59</t>
+          <t>0,0; 14,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,64</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,89</t>
+          <t>0,0; 37,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,85</t>
+          <t>0,0; 21,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 23,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,05</t>
+          <t>0,0; 20,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 17,39</t>
+          <t>1,95; 17,47</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 11,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,24</t>
+          <t>0,92; 4,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,6</t>
+          <t>0,47; 4,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,91</t>
+          <t>0,31; 2,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,99</t>
+          <t>0,51; 3,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,17; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,83; 3,4</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3910</t>
+          <t>0; 3373</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3173</t>
+          <t>0; 3976</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 2935</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 2582</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2756</t>
+          <t>0; 3108</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 4147</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4302</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3623</t>
+          <t>0; 4498</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4982</t>
+          <t>0; 4345</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3485</t>
+          <t>0; 3067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>0; 4915</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5059</t>
+          <t>0; 4006</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2594</t>
+          <t>0; 2776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4852</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4781</t>
+          <t>0; 4632</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2995</t>
+          <t>0; 2719</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2885</t>
+          <t>0; 2894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 4647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3079</t>
+          <t>0; 2815</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>654; 5857</t>
+          <t>656; 5882</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2689</t>
+          <t>0; 2505</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3069</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3043</t>
+          <t>0; 3166</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>0; 3049</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1836; 8510</t>
+          <t>1497; 8050</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>673; 5186</t>
+          <t>672; 6954</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>605; 5577</t>
+          <t>602; 5531</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1371; 8042</t>
+          <t>1373; 8220</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>628; 6243</t>
+          <t>629; 5706</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2576; 10070</t>
+          <t>2575; 10557</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A04-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>3,16%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,11</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 7,03</t>
         </is>
       </c>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,15</t>
+          <t>0,0; 22,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,01</t>
+          <t>0,0; 20,4</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -965,22 +965,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,27 +1018,27 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,95</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,72</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,13</t>
+          <t>0,0; 14,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,04</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>7,82%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,57</t>
+          <t>0,0; 23,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,16</t>
+          <t>0,0; 30,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,47</t>
+          <t>1,97; 15,21</t>
         </is>
       </c>
     </row>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,47; 4,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,95</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,83</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,89</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,9; 5,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,05</t>
+          <t>0,51; 2,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,51</t>
+          <t>0,16; 1,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,4</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos laxantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1760,27 +1760,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1813,27 +1813,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3373</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3976</t>
+          <t>0; 3162</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3097</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1976,27 +1976,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2582</t>
+          <t>0; 2962</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3665</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 4446</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4498</t>
+          <t>0; 4061</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>727</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4345</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3497</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4915</t>
+          <t>0; 4908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4006</t>
+          <t>0; 4082</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2254,22 +2254,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2307,22 +2307,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4460</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2777</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4632</t>
+          <t>0; 4640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 2229</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2901</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 3341</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2796,22 +2796,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>1542</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4647</t>
+          <t>0; 3323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2815</t>
+          <t>0; 5960</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>656; 5882</t>
+          <t>663; 5121</t>
         </is>
       </c>
     </row>
@@ -2901,27 +2901,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2954,27 +2954,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>605</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3841</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2505</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2687</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3166</t>
+          <t>0; 2547</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3049</t>
+          <t>0; 3057</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>4028</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>670; 6599</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>608; 5694</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1497; 8050</t>
+          <t>0; 4795</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>672; 6954</t>
+          <t>0; 5206</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>602; 5531</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>1461; 8802</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1373; 8220</t>
+          <t>1366; 7249</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>629; 5706</t>
+          <t>624; 6247</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2575; 10557</t>
+          <t>2439; 9734</t>
         </is>
       </c>
     </row>
